--- a/templates/enterprise-annual-economic_v1.xlsx
+++ b/templates/enterprise-annual-economic_v1.xlsx
@@ -197,136 +197,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>模板说明</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0">
-      <text>
-        <t>18 位代码；有代码时优先按代码匹配企业</t>
-      </text>
-    </comment>
-    <comment ref="B2" authorId="0" shapeId="0">
-      <text>
-        <t>与营业执照一致；无信用代码时按名称匹配</t>
-      </text>
-    </comment>
-    <comment ref="C2" authorId="0" shapeId="0">
-      <text>
-        <t>四位年份，例如 2025</t>
-      </text>
-    </comment>
-    <comment ref="D2" authorId="0" shapeId="0">
-      <text>
-        <t>统计报表口径</t>
-      </text>
-    </comment>
-    <comment ref="E2" authorId="0" shapeId="0">
-      <text>
-        <t>按不变价计；能源产出率、水资源产出率等均使用此值</t>
-      </text>
-    </comment>
-    <comment ref="F2" authorId="0" shapeId="0">
-      <text>
-        <t>可选</t>
-      </text>
-    </comment>
-    <comment ref="G2" authorId="0" shapeId="0">
-      <text>
-        <t>可选；节能环保产业和新能源产业部分（2024 版指标使用）</t>
-      </text>
-    </comment>
-    <comment ref="H2" authorId="0" shapeId="0">
-      <text>
-        <t>是 / 否</t>
-      </text>
-    </comment>
-    <comment ref="I2" authorId="0" shapeId="0">
-      <text>
-        <t>是 / 否；计入“高新技术企业工业总产值占比”</t>
-      </text>
-    </comment>
-    <comment ref="J2" authorId="0" shapeId="0">
-      <text>
-        <t>如 GR2023…</t>
-      </text>
-    </comment>
-    <comment ref="K2" authorId="0" shapeId="0">
-      <text>
-        <t>从下拉列表选择，用于标记数据质量</t>
-      </text>
-    </comment>
-    <comment ref="L2" authorId="0" shapeId="0">
-      <text>
-        <t>可选</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>模板说明</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0">
-      <text>
-        <t>18 位代码；有代码时优先按代码匹配企业</t>
-      </text>
-    </comment>
-    <comment ref="B2" authorId="0" shapeId="0">
-      <text>
-        <t>与营业执照一致；无信用代码时按名称匹配</t>
-      </text>
-    </comment>
-    <comment ref="C2" authorId="0" shapeId="0">
-      <text>
-        <t>四位年份，例如 2025</t>
-      </text>
-    </comment>
-    <comment ref="D2" authorId="0" shapeId="0">
-      <text>
-        <t>与能耗限额标准中的产品名称尽量一致，一种产品一行</t>
-      </text>
-    </comment>
-    <comment ref="E2" authorId="0" shapeId="0">
-      <text>
-        <t>合格产品产量</t>
-      </text>
-    </comment>
-    <comment ref="F2" authorId="0" shapeId="0">
-      <text>
-        <t>如 m3、t、万只、件；与产量对应</t>
-      </text>
-    </comment>
-    <comment ref="G2" authorId="0" shapeId="0">
-      <text>
-        <t>可选；企业自算的单位产品综合能耗</t>
-      </text>
-    </comment>
-    <comment ref="H2" authorId="0" shapeId="0">
-      <text>
-        <t>可选；如 GB 3xxxx-20xx</t>
-      </text>
-    </comment>
-    <comment ref="I2" authorId="0" shapeId="0">
-      <text>
-        <t>从下拉列表选择，用于标记数据质量</t>
-      </text>
-    </comment>
-    <comment ref="J2" authorId="0" shapeId="0">
-      <text>
-        <t>可选</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8303,7 +8173,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -14398,6 +14267,5 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/templates/enterprise-annual-economic_v1.xlsx
+++ b/templates/enterprise-annual-economic_v1.xlsx
@@ -678,7 +678,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>从业人员年平均人数（人）</t>
+          <t>年末从业人数（人）</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>可选</t>
+          <t>可选；年末工业企业从业人数（人均工业增加值的分母）</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -1070,7 +1070,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>从业人员年平均人数（人）</t>
+          <t>年末从业人数（人）</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">

--- a/templates/enterprise-annual-economic_v1.xlsx
+++ b/templates/enterprise-annual-economic_v1.xlsx
@@ -8168,8 +8168,8 @@
     <dataValidation sqref="I3:I502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请从下拉列表选择" error="取值：否、是" type="list">
       <formula1>"否,是"</formula1>
     </dataValidation>
-    <dataValidation sqref="K3:K502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="请从下拉列表选择" error="取值：系统导出、统计报表、财务报表" type="list">
-      <formula1>"系统导出,统计报表,财务报表"</formula1>
+    <dataValidation sqref="K3:K502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="请从下拉列表选择" error="取值：公开报道、系统导出、统计报表、财务报表" type="list">
+      <formula1>"公开报道,系统导出,统计报表,财务报表"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14262,8 +14262,8 @@
     <dataValidation sqref="E3:E502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请填写数值" error="请填写不小于 0 的数字，不要带单位" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="I3:I502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="请从下拉列表选择" error="取值：生产台账、系统导出、统计报表" type="list">
-      <formula1>"生产台账,系统导出,统计报表"</formula1>
+    <dataValidation sqref="I3:I502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="请从下拉列表选择" error="取值：公开报道、生产台账、系统导出、统计报表" type="list">
+      <formula1>"公开报道,生产台账,系统导出,统计报表"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
